--- a/artfynd/A 50207-2022 artfynd.xlsx
+++ b/artfynd/A 50207-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50207-2022 artfynd.xlsx
+++ b/artfynd/A 50207-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1250,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112610291</v>
+        <v>112610294</v>
       </c>
       <c r="B7" t="n">
-        <v>91032</v>
+        <v>77609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,25 +1262,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1290,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>425870</v>
+        <v>425903</v>
       </c>
       <c r="R7" t="n">
-        <v>6818065</v>
+        <v>6818068</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112610294</v>
+        <v>112610296</v>
       </c>
       <c r="B8" t="n">
-        <v>77609</v>
+        <v>77608</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,21 +1373,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>425903</v>
+        <v>425904</v>
       </c>
       <c r="R8" t="n">
-        <v>6818068</v>
+        <v>6818070</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,113 +1461,6 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>112610296</v>
-      </c>
-      <c r="B9" t="n">
-        <v>77608</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>6446</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Carbonicola anthracophila</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Trängslet, Dlr</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>425904</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6818070</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Älvdalen</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Älvdalen</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2022-10-05</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2022-10-05</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
